--- a/AAII_Financials/Yearly/OGAA_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/OGAA_YR_FIN.xlsx
@@ -5,7 +5,7 @@
   <workbookPr codeName="ThisWorkbook" defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Stocks_Automation\AAII_Financials\Yearly\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\sundeep\Private\Investing\Automation\AAII\AAII_Financials\Yearly\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -17,12 +17,12 @@
   <definedNames>
     <definedName name="Ticker">#REF!</definedName>
   </definedNames>
-  <calcPr calcId="152511" calcMode="manual" concurrentCalc="0"/>
+  <calcPr calcId="152511" calcMode="manual"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="264" uniqueCount="92">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="252" uniqueCount="92">
   <si>
     <t>OGAA</t>
   </si>
@@ -949,8 +949,8 @@
       <c r="C15" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="D15" s="3" t="s">
-        <v>3</v>
+      <c r="D15" s="3">
+        <v>0</v>
       </c>
       <c r="E15" s="3">
         <v>0</v>
@@ -998,11 +998,11 @@
       <c r="C17" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>3</v>
+      <c r="D17" s="3">
+        <v>900</v>
       </c>
       <c r="E17" s="3">
-        <v>1500</v>
+        <v>1400</v>
       </c>
       <c r="F17" s="3">
         <v>300</v>
@@ -1034,11 +1034,11 @@
       <c r="C18" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>3</v>
+      <c r="D18" s="3">
+        <v>-600</v>
       </c>
       <c r="E18" s="3">
-        <v>-1200</v>
+        <v>-1100</v>
       </c>
       <c r="F18" s="3">
         <v>-200</v>
@@ -1086,8 +1086,8 @@
       <c r="C20" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>3</v>
+      <c r="D20" s="3">
+        <v>0</v>
       </c>
       <c r="E20" s="3">
         <v>0</v>
@@ -1122,11 +1122,11 @@
       <c r="C21" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>3</v>
+      <c r="D21" s="3">
+        <v>-600</v>
       </c>
       <c r="E21" s="3">
-        <v>-1200</v>
+        <v>-1000</v>
       </c>
       <c r="F21" s="3">
         <v>-200</v>
@@ -1137,8 +1137,8 @@
       <c r="H21" s="3">
         <v>-800</v>
       </c>
-      <c r="I21" s="3" t="s">
-        <v>3</v>
+      <c r="I21" s="3">
+        <v>0</v>
       </c>
       <c r="J21" s="3" t="s">
         <v>3</v>
@@ -1198,7 +1198,7 @@
         <v>-600</v>
       </c>
       <c r="E23" s="3">
-        <v>-1200</v>
+        <v>-1000</v>
       </c>
       <c r="F23" s="3">
         <v>-200</v>
@@ -1302,11 +1302,11 @@
       <c r="C26" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="D26" s="3" t="s">
-        <v>3</v>
+      <c r="D26" s="3">
+        <v>-600</v>
       </c>
       <c r="E26" s="3">
-        <v>-1200</v>
+        <v>-1000</v>
       </c>
       <c r="F26" s="3">
         <v>-200</v>
@@ -1338,11 +1338,11 @@
       <c r="C27" s="1" t="s">
         <v>22</v>
       </c>
-      <c r="D27" s="3" t="s">
-        <v>3</v>
+      <c r="D27" s="3">
+        <v>-600</v>
       </c>
       <c r="E27" s="3">
-        <v>-1100</v>
+        <v>-1000</v>
       </c>
       <c r="F27" s="3">
         <v>-200</v>
@@ -1411,10 +1411,10 @@
         <v>24</v>
       </c>
       <c r="D29" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="E29" s="3">
-        <v>0</v>
+        <v>-100</v>
       </c>
       <c r="F29" s="3">
         <v>-700</v>
@@ -1518,8 +1518,8 @@
       <c r="C32" s="1" t="s">
         <v>27</v>
       </c>
-      <c r="D32" s="3" t="s">
-        <v>3</v>
+      <c r="D32" s="3">
+        <v>0</v>
       </c>
       <c r="E32" s="3">
         <v>0</v>
@@ -1554,8 +1554,8 @@
       <c r="C33" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>3</v>
+      <c r="D33" s="3">
+        <v>-600</v>
       </c>
       <c r="E33" s="3">
         <v>-1100</v>
@@ -1626,8 +1626,8 @@
       <c r="C35" s="1" t="s">
         <v>30</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>3</v>
+      <c r="D35" s="3">
+        <v>-600</v>
       </c>
       <c r="E35" s="3">
         <v>-1100</v>
@@ -2344,7 +2344,7 @@
         <v>52</v>
       </c>
       <c r="D59" s="3">
-        <v>400</v>
+        <v>200</v>
       </c>
       <c r="E59" s="3">
         <v>400</v>
@@ -3048,8 +3048,8 @@
       <c r="C81" s="1" t="s">
         <v>28</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>3</v>
+      <c r="D81" s="3">
+        <v>-600</v>
       </c>
       <c r="E81" s="3">
         <v>-1100</v>
@@ -3712,7 +3712,7 @@
         <v>0</v>
       </c>
       <c r="E101" s="3">
-        <v>0</v>
+        <v>100</v>
       </c>
       <c r="F101" s="3">
         <v>-200</v>
@@ -3745,7 +3745,7 @@
         <v>91</v>
       </c>
       <c r="D102" s="3">
-        <v>400</v>
+        <v>-400</v>
       </c>
       <c r="E102" s="3">
         <v>300</v>
